--- a/Annexes_renommage_ajoutNomcenclaturesRef/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/Annexes_renommage_ajoutNomcenclaturesRef/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-06T17:12:19+00:00</t>
+    <t>2024-06-06T17:52:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/Annexes_renommage_ajoutNomcenclaturesRef/ig/StructureDefinition-tddui-documentreference.xlsx
+++ b/Annexes_renommage_ajoutNomcenclaturesRef/ig/StructureDefinition-tddui-documentreference.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-06T17:52:23+00:00</t>
+    <t>2024-06-06T18:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
